--- a/exports/trend_1d/AMBUJACEM_full_report.xlsx
+++ b/exports/trend_1d/AMBUJACEM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42080</v>
+        <v>42081</v>
       </c>
       <c r="H2" t="n">
-        <v>258.7</v>
+        <v>252.7</v>
       </c>
       <c r="I2" t="n">
         <v>255.6961766345122</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K2" t="n">
-        <v>7.59</v>
+        <v>5.09</v>
       </c>
       <c r="L2" t="n">
         <v>2.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.45</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42186</v>
+        <v>42187</v>
       </c>
       <c r="H3" t="n">
-        <v>238.15</v>
+        <v>239.85</v>
       </c>
       <c r="I3" t="n">
         <v>239.4106841915581</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K3" t="n">
-        <v>5.76</v>
+        <v>5.09</v>
       </c>
       <c r="L3" t="n">
         <v>5.4</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.77</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42212</v>
+        <v>42213</v>
       </c>
       <c r="H4" t="n">
-        <v>234.05</v>
+        <v>230.2</v>
       </c>
       <c r="I4" t="n">
         <v>233.6951390039271</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.42</v>
+        <v>-4.02</v>
       </c>
       <c r="L4" t="n">
-        <v>3.21</v>
+        <v>4.9</v>
       </c>
       <c r="M4" t="n">
         <v>2.17</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.91</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42366</v>
+        <v>42367</v>
       </c>
       <c r="H5" t="n">
-        <v>202.7</v>
+        <v>205.55</v>
       </c>
       <c r="I5" t="n">
         <v>203.6263743895292</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K5" t="n">
-        <v>11.95</v>
+        <v>10.71</v>
       </c>
       <c r="L5" t="n">
         <v>3.34</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>6.71</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H6" t="n">
-        <v>193.9</v>
+        <v>191.1</v>
       </c>
       <c r="I6" t="n">
         <v>193.5258687709484</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.67</v>
+        <v>-7.03</v>
       </c>
       <c r="L6" t="n">
-        <v>6.35</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M6" t="n">
         <v>1.94</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.23</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42437</v>
+        <v>42438</v>
       </c>
       <c r="H7" t="n">
-        <v>201.65</v>
+        <v>204.35</v>
       </c>
       <c r="I7" t="n">
         <v>203.4235898484989</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.52</v>
+        <v>-6.93</v>
       </c>
       <c r="L7" t="n">
-        <v>6.99</v>
+        <v>7.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.37</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42508</v>
+        <v>42509</v>
       </c>
       <c r="H8" t="n">
-        <v>216.65</v>
+        <v>213.65</v>
       </c>
       <c r="I8" t="n">
         <v>214.3704970468971</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K8" t="n">
-        <v>6.02</v>
+        <v>4.55</v>
       </c>
       <c r="L8" t="n">
         <v>2.3</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.11</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42516</v>
+        <v>42517</v>
       </c>
       <c r="H9" t="n">
-        <v>224.6</v>
+        <v>230.25</v>
       </c>
       <c r="I9" t="n">
         <v>226.074234919103</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.13</v>
+        <v>-7.77</v>
       </c>
       <c r="L9" t="n">
-        <v>7.42</v>
+        <v>8.59</v>
       </c>
       <c r="M9" t="n">
         <v>0.84</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.87</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42636</v>
+        <v>42639</v>
       </c>
       <c r="H10" t="n">
-        <v>259</v>
+        <v>254.85</v>
       </c>
       <c r="I10" t="n">
         <v>257.2884590877064</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K10" t="n">
-        <v>12.49</v>
+        <v>10.68</v>
       </c>
       <c r="L10" t="n">
         <v>1.85</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.87</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H11" t="n">
-        <v>206.3</v>
+        <v>214.6</v>
       </c>
       <c r="I11" t="n">
         <v>214.1890101637248</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K11" t="n">
-        <v>19.05</v>
+        <v>15.79</v>
       </c>
       <c r="L11" t="n">
         <v>3.2</v>
@@ -1068,7 +1199,7 @@
         <v>1.89</v>
       </c>
       <c r="N11" t="n">
-        <v>2.84</v>
+        <v>4.02</v>
       </c>
       <c r="O11" t="n">
         <v>-1.6</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.58</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H12" t="n">
-        <v>239.8</v>
+        <v>235.3</v>
       </c>
       <c r="I12" t="n">
         <v>239.2334396788399</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K12" t="n">
-        <v>11.74</v>
+        <v>9.65</v>
       </c>
       <c r="L12" t="n">
         <v>3.03</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>9.73</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42919</v>
+        <v>42920</v>
       </c>
       <c r="H13" t="n">
-        <v>247.45</v>
+        <v>249.1</v>
       </c>
       <c r="I13" t="n">
         <v>247.6344159414788</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.16</v>
+        <v>-5.86</v>
       </c>
       <c r="L13" t="n">
-        <v>6.1</v>
+        <v>7.39</v>
       </c>
       <c r="M13" t="n">
-        <v>0.83</v>
+        <v>1.84</v>
       </c>
       <c r="N13" t="n">
         <v>2.04</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.74</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H14" t="n">
-        <v>269.9</v>
+        <v>262.25</v>
       </c>
       <c r="I14" t="n">
         <v>269.3869009389189</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K14" t="n">
-        <v>8.35</v>
+        <v>5.28</v>
       </c>
       <c r="L14" t="n">
         <v>7.37</v>
@@ -1239,7 +1406,7 @@
         <v>1.63</v>
       </c>
       <c r="N14" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
         <v>0.67</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43024</v>
+        <v>43025</v>
       </c>
       <c r="H15" t="n">
-        <v>279.8</v>
+        <v>280.85</v>
       </c>
       <c r="I15" t="n">
         <v>280.8252674044245</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.69</v>
+        <v>-7.09</v>
       </c>
       <c r="L15" t="n">
-        <v>7.66</v>
+        <v>8.06</v>
       </c>
       <c r="M15" t="n">
         <v>0.6899999999999999</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.37</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43056</v>
+        <v>43059</v>
       </c>
       <c r="H16" t="n">
-        <v>274.5</v>
+        <v>264.7</v>
       </c>
       <c r="I16" t="n">
         <v>265.8623180506064</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.26</v>
+        <v>-5.75</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>6.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.33</v>
       </c>
       <c r="N16" t="n">
-        <v>1.88</v>
+        <v>3.57</v>
       </c>
       <c r="O16" t="n">
         <v>0.38</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.06</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43108</v>
+        <v>43109</v>
       </c>
       <c r="H17" t="n">
-        <v>274.6</v>
+        <v>277.15</v>
       </c>
       <c r="I17" t="n">
         <v>276.4351348128617</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.74</v>
+        <v>-4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>4.87</v>
+        <v>5.53</v>
       </c>
       <c r="M17" t="n">
         <v>0.87</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>6.48</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43133</v>
+        <v>43136</v>
       </c>
       <c r="H18" t="n">
-        <v>259.55</v>
+        <v>259.1</v>
       </c>
       <c r="I18" t="n">
         <v>259.5320086357926</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.35</v>
+        <v>-6.51</v>
       </c>
       <c r="L18" t="n">
-        <v>7.23</v>
+        <v>9.06</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="N18" t="n">
         <v>2.59</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.56</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43208</v>
+        <v>43209</v>
       </c>
       <c r="H19" t="n">
-        <v>244.9</v>
+        <v>247</v>
       </c>
       <c r="I19" t="n">
         <v>245.641971656127</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K19" t="n">
-        <v>5.48</v>
+        <v>4.67</v>
       </c>
       <c r="L19" t="n">
         <v>4.09</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.29</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="H20" t="n">
-        <v>235.25</v>
+        <v>229.45</v>
       </c>
       <c r="I20" t="n">
         <v>232.7910940789409</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.76</v>
+        <v>-7.11</v>
       </c>
       <c r="L20" t="n">
-        <v>5.63</v>
+        <v>7.39</v>
       </c>
       <c r="M20" t="n">
         <v>0.53</v>
       </c>
       <c r="N20" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
         <v>0.86</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.52</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43276</v>
+        <v>43277</v>
       </c>
       <c r="H21" t="n">
-        <v>206.8</v>
+        <v>211.95</v>
       </c>
       <c r="I21" t="n">
         <v>211.023996086889</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K21" t="n">
-        <v>9.869999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="L21" t="n">
         <v>2.96</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H22" t="n">
-        <v>196.9</v>
+        <v>190.55</v>
       </c>
       <c r="I22" t="n">
         <v>194.4045568526579</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.1</v>
+        <v>-10.1</v>
       </c>
       <c r="L22" t="n">
-        <v>7.38</v>
+        <v>10.57</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="N22" t="n">
         <v>3.64</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>11.32</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H23" t="n">
-        <v>198</v>
+        <v>212.65</v>
       </c>
       <c r="I23" t="n">
         <v>210.8820420643692</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.91</v>
+        <v>-11.6</v>
       </c>
       <c r="L23" t="n">
-        <v>5.3</v>
+        <v>13.78</v>
       </c>
       <c r="M23" t="n">
-        <v>0.43</v>
+        <v>2.27</v>
       </c>
       <c r="N23" t="n">
-        <v>2.65</v>
+        <v>7.4</v>
       </c>
       <c r="O23" t="n">
         <v>-3.22</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.48</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43350</v>
+        <v>43353</v>
       </c>
       <c r="H24" t="n">
-        <v>227.5</v>
+        <v>219.7</v>
       </c>
       <c r="I24" t="n">
         <v>220.3282958210668</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K24" t="n">
-        <v>6.98</v>
+        <v>3.32</v>
       </c>
       <c r="L24" t="n">
         <v>4.77</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.98</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43418</v>
+        <v>43419</v>
       </c>
       <c r="H25" t="n">
-        <v>211.2</v>
+        <v>217.85</v>
       </c>
       <c r="I25" t="n">
         <v>217.022193528865</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K25" t="n">
-        <v>3.87</v>
+        <v>0.84</v>
       </c>
       <c r="L25" t="n">
         <v>6.87</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.78</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H26" t="n">
-        <v>211.2</v>
+        <v>202.35</v>
       </c>
       <c r="I26" t="n">
         <v>206.9136509434694</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.05</v>
+        <v>-7.11</v>
       </c>
       <c r="L26" t="n">
         <v>8.08</v>
@@ -1923,7 +2234,7 @@
         <v>2.27</v>
       </c>
       <c r="N26" t="n">
-        <v>3.92</v>
+        <v>4.19</v>
       </c>
       <c r="O26" t="n">
         <v>3.15</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>10.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H27" t="n">
-        <v>217.45</v>
+        <v>222</v>
       </c>
       <c r="I27" t="n">
         <v>217.8892723535967</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.46</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>8.380000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="M27" t="n">
         <v>0.61</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43591</v>
+        <v>43592</v>
       </c>
       <c r="H28" t="n">
-        <v>219.7</v>
+        <v>218.2</v>
       </c>
       <c r="I28" t="n">
         <v>219.1056548130394</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.04</v>
+        <v>-1.71</v>
       </c>
       <c r="L28" t="n">
         <v>2.68</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H29" t="n">
-        <v>222.55</v>
+        <v>231.65</v>
       </c>
       <c r="I29" t="n">
         <v>228.9542467922882</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.99</v>
+        <v>-6.16</v>
       </c>
       <c r="L29" t="n">
-        <v>5.77</v>
+        <v>6.69</v>
       </c>
       <c r="M29" t="n">
         <v>2.28</v>
       </c>
       <c r="N29" t="n">
-        <v>2.62</v>
+        <v>4.09</v>
       </c>
       <c r="O29" t="n">
         <v>-0.68</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>11.04</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H30" t="n">
-        <v>220.45</v>
+        <v>214.2</v>
       </c>
       <c r="I30" t="n">
         <v>216.753205542005</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.83</v>
+        <v>-7.53</v>
       </c>
       <c r="L30" t="n">
-        <v>6.69</v>
+        <v>7.94</v>
       </c>
       <c r="M30" t="n">
         <v>1.66</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.17</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H31" t="n">
-        <v>191.8</v>
+        <v>215.2</v>
       </c>
       <c r="I31" t="n">
         <v>209.045067789152</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K31" t="n">
-        <v>10.46</v>
+        <v>-0.47</v>
       </c>
       <c r="L31" t="n">
         <v>4.48</v>
@@ -2208,7 +2579,7 @@
         <v>2.58</v>
       </c>
       <c r="N31" t="n">
-        <v>3.51</v>
+        <v>12.2</v>
       </c>
       <c r="O31" t="n">
         <v>-2.84</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>15.71</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H32" t="n">
-        <v>199.85</v>
+        <v>196.35</v>
       </c>
       <c r="I32" t="n">
         <v>197.0426925205375</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-7.13</v>
+        <v>-8.76</v>
       </c>
       <c r="L32" t="n">
         <v>11.13</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="N32" t="n">
         <v>2.62</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.23</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43838</v>
+        <v>43839</v>
       </c>
       <c r="H33" t="n">
-        <v>201.65</v>
+        <v>207.95</v>
       </c>
       <c r="I33" t="n">
         <v>207.1526581127378</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.7</v>
+        <v>-5.91</v>
       </c>
       <c r="L33" t="n">
         <v>7.46</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>8.49</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H34" t="n">
-        <v>204.5</v>
+        <v>195.35</v>
       </c>
       <c r="I34" t="n">
         <v>201.8616619997849</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.66</v>
+        <v>-6.06</v>
       </c>
       <c r="L34" t="n">
-        <v>2.14</v>
+        <v>6.71</v>
       </c>
       <c r="M34" t="n">
         <v>0.63</v>
       </c>
       <c r="N34" t="n">
-        <v>2.57</v>
+        <v>4.47</v>
       </c>
       <c r="O34" t="n">
         <v>3.12</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>12.46</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43963</v>
+        <v>43964</v>
       </c>
       <c r="H35" t="n">
-        <v>175.2</v>
+        <v>183</v>
       </c>
       <c r="I35" t="n">
         <v>181.1970437130026</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K35" t="n">
-        <v>10.31</v>
+        <v>6.32</v>
       </c>
       <c r="L35" t="n">
         <v>10.85</v>
       </c>
       <c r="M35" t="n">
-        <v>3.89</v>
+        <v>3.94</v>
       </c>
       <c r="N35" t="n">
         <v>6.98</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.24</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44077</v>
+        <v>44078</v>
       </c>
       <c r="H36" t="n">
-        <v>214.6</v>
+        <v>208.5</v>
       </c>
       <c r="I36" t="n">
         <v>209.7834170630169</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K36" t="n">
-        <v>17.27</v>
+        <v>13.93</v>
       </c>
       <c r="L36" t="n">
         <v>6.97</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H37" t="n">
-        <v>221.35</v>
+        <v>225.3</v>
       </c>
       <c r="I37" t="n">
         <v>224.7218993211246</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.16</v>
+        <v>-8.06</v>
       </c>
       <c r="L37" t="n">
-        <v>7.53</v>
+        <v>9.23</v>
       </c>
       <c r="M37" t="n">
         <v>1.74</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H38" t="n">
-        <v>251.05</v>
+        <v>235.4</v>
       </c>
       <c r="I38" t="n">
         <v>242.6890396492099</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K38" t="n">
-        <v>11.43</v>
+        <v>4.48</v>
       </c>
       <c r="L38" t="n">
         <v>2.31</v>
@@ -2607,7 +3062,7 @@
         <v>4.75</v>
       </c>
       <c r="N38" t="n">
-        <v>3.27</v>
+        <v>6.23</v>
       </c>
       <c r="O38" t="n">
         <v>1.78</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>11.87</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44201</v>
+        <v>44202</v>
       </c>
       <c r="H39" t="n">
-        <v>254.2</v>
+        <v>261.1</v>
       </c>
       <c r="I39" t="n">
         <v>259.1999711761016</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.99</v>
+        <v>-10.92</v>
       </c>
       <c r="L39" t="n">
-        <v>10.83</v>
+        <v>11.3</v>
       </c>
       <c r="M39" t="n">
         <v>7.5</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.32</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H40" t="n">
-        <v>248</v>
+        <v>243.35</v>
       </c>
       <c r="I40" t="n">
         <v>247.9555181695645</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.02</v>
+        <v>-6.8</v>
       </c>
       <c r="L40" t="n">
-        <v>5.78</v>
+        <v>7.41</v>
       </c>
       <c r="M40" t="n">
         <v>0.99</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.34</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44228</v>
+        <v>44229</v>
       </c>
       <c r="H41" t="n">
-        <v>260.8</v>
+        <v>276.25</v>
       </c>
       <c r="I41" t="n">
         <v>273.379856051796</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.17</v>
+        <v>-13.52</v>
       </c>
       <c r="L41" t="n">
-        <v>7.66</v>
+        <v>14.9</v>
       </c>
       <c r="M41" t="n">
         <v>1.51</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>13.93</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H42" t="n">
-        <v>409.4</v>
+        <v>391.8</v>
       </c>
       <c r="I42" t="n">
         <v>392.8494484633879</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K42" t="n">
-        <v>48.2</v>
+        <v>41.83</v>
       </c>
       <c r="L42" t="n">
         <v>5.48</v>
@@ -2835,7 +3338,7 @@
         <v>1.9</v>
       </c>
       <c r="N42" t="n">
-        <v>3.81</v>
+        <v>4.3</v>
       </c>
       <c r="O42" t="n">
         <v>5.92</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.49</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44440</v>
+        <v>44441</v>
       </c>
       <c r="H43" t="n">
-        <v>421.5</v>
+        <v>428.7</v>
       </c>
       <c r="I43" t="n">
         <v>425.0959988512599</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.58</v>
+        <v>-9.42</v>
       </c>
       <c r="L43" t="n">
-        <v>8.23</v>
+        <v>10.26</v>
       </c>
       <c r="M43" t="n">
         <v>1.25</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>7.81</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44467</v>
+        <v>44468</v>
       </c>
       <c r="H44" t="n">
-        <v>413.1</v>
+        <v>406.45</v>
       </c>
       <c r="I44" t="n">
         <v>409.4399047814467</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.64</v>
+        <v>-5.19</v>
       </c>
       <c r="L44" t="n">
-        <v>6.13</v>
+        <v>6.43</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="N44" t="n">
         <v>2.42</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.83</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44498</v>
+        <v>44501</v>
       </c>
       <c r="H45" t="n">
-        <v>404.8</v>
+        <v>409.8</v>
       </c>
       <c r="I45" t="n">
         <v>405.6996843077279</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K45" t="n">
-        <v>0.41</v>
+        <v>-0.82</v>
       </c>
       <c r="L45" t="n">
         <v>2.84</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H46" t="n">
-        <v>400.85</v>
+        <v>388.7</v>
       </c>
       <c r="I46" t="n">
         <v>396.9464549267315</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.18</v>
+        <v>-5.15</v>
       </c>
       <c r="L46" t="n">
-        <v>3.25</v>
+        <v>6.05</v>
       </c>
       <c r="M46" t="n">
         <v>0.85</v>
       </c>
       <c r="N46" t="n">
-        <v>2.72</v>
+        <v>3.03</v>
       </c>
       <c r="O46" t="n">
         <v>1.24</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.3</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H47" t="n">
-        <v>377.5</v>
+        <v>387</v>
       </c>
       <c r="I47" t="n">
         <v>385.9006615902775</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K47" t="n">
-        <v>2.88</v>
+        <v>0.44</v>
       </c>
       <c r="L47" t="n">
         <v>3.64</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.52</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H48" t="n">
-        <v>375.1</v>
+        <v>368.65</v>
       </c>
       <c r="I48" t="n">
         <v>372.7724387769206</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.07</v>
+        <v>-4.74</v>
       </c>
       <c r="L48" t="n">
-        <v>3.76</v>
+        <v>5.93</v>
       </c>
       <c r="M48" t="n">
         <v>0.91</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44656</v>
+        <v>44657</v>
       </c>
       <c r="H49" t="n">
-        <v>316.8</v>
+        <v>320.7</v>
       </c>
       <c r="I49" t="n">
         <v>319.6585895134812</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K49" t="n">
-        <v>14.06</v>
+        <v>13.01</v>
       </c>
       <c r="L49" t="n">
         <v>4.79</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.48</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44834</v>
+        <v>44837</v>
       </c>
       <c r="H50" t="n">
-        <v>515.6</v>
+        <v>488.65</v>
       </c>
       <c r="I50" t="n">
         <v>497.4612576091793</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K50" t="n">
-        <v>60.77</v>
+        <v>52.37</v>
       </c>
       <c r="L50" t="n">
         <v>1.64</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>7</v>
+      </c>
+      <c r="U50" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>20.55</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="H51" t="n">
-        <v>557.55</v>
+        <v>580.3</v>
       </c>
       <c r="I51" t="n">
         <v>575.5744747810897</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>-14.1</v>
+        <v>-18.76</v>
       </c>
       <c r="L51" t="n">
-        <v>18.84</v>
+        <v>20.03</v>
       </c>
       <c r="M51" t="n">
         <v>2.81</v>
       </c>
       <c r="N51" t="n">
-        <v>3.73</v>
+        <v>4.08</v>
       </c>
       <c r="O51" t="n">
         <v>-5.23</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>10.88</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H52" t="n">
-        <v>560.1</v>
+        <v>539.2</v>
       </c>
       <c r="I52" t="n">
         <v>546.3728385881438</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.48</v>
+        <v>-7.08</v>
       </c>
       <c r="L52" t="n">
-        <v>4.62</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M52" t="n">
         <v>0.57</v>
       </c>
       <c r="N52" t="n">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
       <c r="O52" t="n">
         <v>4.08</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.31</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45050</v>
+        <v>45051</v>
       </c>
       <c r="H53" t="n">
-        <v>388.3</v>
+        <v>400.55</v>
       </c>
       <c r="I53" t="n">
         <v>399.645588335838</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K53" t="n">
-        <v>27.99</v>
+        <v>25.71</v>
       </c>
       <c r="L53" t="n">
         <v>4.6</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>6</v>
+      </c>
+      <c r="U53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.23</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H54" t="n">
-        <v>444.85</v>
+        <v>425.8</v>
       </c>
       <c r="I54" t="n">
         <v>433.1840292168554</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K54" t="n">
-        <v>11.06</v>
+        <v>6.3</v>
       </c>
       <c r="L54" t="n">
         <v>3.27</v>
@@ -3519,7 +4166,7 @@
         <v>0.39</v>
       </c>
       <c r="N54" t="n">
-        <v>1.78</v>
+        <v>4.28</v>
       </c>
       <c r="O54" t="n">
         <v>3.15</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>9.91</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45132</v>
+        <v>45133</v>
       </c>
       <c r="H55" t="n">
-        <v>440.1</v>
+        <v>443.5</v>
       </c>
       <c r="I55" t="n">
         <v>441.9744986375981</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.36</v>
+        <v>-4.16</v>
       </c>
       <c r="L55" t="n">
-        <v>4.51</v>
+        <v>5.3</v>
       </c>
       <c r="M55" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="N55" t="n">
         <v>4.1</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.94</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45162</v>
+        <v>45163</v>
       </c>
       <c r="H56" t="n">
-        <v>448.95</v>
+        <v>434.6</v>
       </c>
       <c r="I56" t="n">
         <v>436.3281930985669</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K56" t="n">
-        <v>1.23</v>
+        <v>-2.01</v>
       </c>
       <c r="L56" t="n">
-        <v>2.57</v>
+        <v>3.02</v>
       </c>
       <c r="M56" t="n">
         <v>1.28</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.72</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="H57" t="n">
-        <v>431.2</v>
+        <v>435.65</v>
       </c>
       <c r="I57" t="n">
         <v>434.8284288893583</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K57" t="n">
-        <v>0.78</v>
+        <v>-0.24</v>
       </c>
       <c r="L57" t="n">
         <v>4.44</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.6</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H58" t="n">
-        <v>587.55</v>
+        <v>559.25</v>
       </c>
       <c r="I58" t="n">
         <v>572.9299584818715</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K58" t="n">
-        <v>34.87</v>
+        <v>28.37</v>
       </c>
       <c r="L58" t="n">
         <v>1.74</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>11.51</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H59" t="n">
-        <v>621.5</v>
+        <v>634.7</v>
       </c>
       <c r="I59" t="n">
         <v>623.6397943160398</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>-11.13</v>
+        <v>-13.49</v>
       </c>
       <c r="L59" t="n">
-        <v>12.05</v>
+        <v>13.92</v>
       </c>
       <c r="M59" t="n">
         <v>1.15</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>9.15</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H60" t="n">
-        <v>594.55</v>
+        <v>574.3</v>
       </c>
       <c r="I60" t="n">
         <v>589.4620992958495</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.33</v>
+        <v>-9.52</v>
       </c>
       <c r="L60" t="n">
-        <v>7.36</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M60" t="n">
         <v>1.45</v>
       </c>
       <c r="N60" t="n">
-        <v>2.69</v>
+        <v>3.41</v>
       </c>
       <c r="O60" t="n">
         <v>2.12</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>11.46</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45434</v>
+        <v>45435</v>
       </c>
       <c r="H61" t="n">
-        <v>633.05</v>
+        <v>646.5</v>
       </c>
       <c r="I61" t="n">
         <v>633.9011186104162</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.23</v>
+        <v>-12.57</v>
       </c>
       <c r="L61" t="n">
-        <v>10.7</v>
+        <v>12.89</v>
       </c>
       <c r="M61" t="n">
         <v>0.39</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H62" t="n">
-        <v>670.8</v>
+        <v>556.6</v>
       </c>
       <c r="I62" t="n">
         <v>607.4194231743609</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K62" t="n">
-        <v>3.76</v>
+        <v>-13.91</v>
       </c>
       <c r="L62" t="n">
-        <v>4.66</v>
+        <v>19.82</v>
       </c>
       <c r="M62" t="n">
         <v>0.49</v>
       </c>
       <c r="N62" t="n">
-        <v>1.74</v>
+        <v>17.02</v>
       </c>
       <c r="O62" t="n">
         <v>2.12</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>24.38</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45471</v>
+        <v>45474</v>
       </c>
       <c r="H63" t="n">
-        <v>670.25</v>
+        <v>695</v>
       </c>
       <c r="I63" t="n">
         <v>679.4127672287677</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K63" t="n">
-        <v>-20.42</v>
+        <v>-24.87</v>
       </c>
       <c r="L63" t="n">
-        <v>23.79</v>
+        <v>26.09</v>
       </c>
       <c r="M63" t="n">
         <v>3.69</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>12.08</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H64" t="n">
-        <v>636.15</v>
+        <v>625.55</v>
       </c>
       <c r="I64" t="n">
         <v>632.8730225874734</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K64" t="n">
-        <v>-8.470000000000001</v>
+        <v>-9.99</v>
       </c>
       <c r="L64" t="n">
-        <v>8.81</v>
+        <v>10.37</v>
       </c>
       <c r="M64" t="n">
         <v>0.89</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.63</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H65" t="n">
-        <v>538.8</v>
+        <v>566.55</v>
       </c>
       <c r="I65" t="n">
         <v>543.5580827003819</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K65" t="n">
-        <v>13.87</v>
+        <v>9.43</v>
       </c>
       <c r="L65" t="n">
         <v>5.51</v>
@@ -4146,7 +4925,7 @@
         <v>3.83</v>
       </c>
       <c r="N65" t="n">
-        <v>4.31</v>
+        <v>5.15</v>
       </c>
       <c r="O65" t="n">
         <v>-1.67</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>13.84</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H66" t="n">
-        <v>548.7</v>
+        <v>529.9</v>
       </c>
       <c r="I66" t="n">
         <v>531.7915449352422</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.15</v>
+        <v>-6.47</v>
       </c>
       <c r="L66" t="n">
-        <v>6.35</v>
+        <v>7.14</v>
       </c>
       <c r="M66" t="n">
         <v>1.56</v>
       </c>
       <c r="N66" t="n">
-        <v>2.57</v>
+        <v>3.43</v>
       </c>
       <c r="O66" t="n">
         <v>5.15</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>9.15</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="H67" t="n">
-        <v>536.65</v>
+        <v>548.8</v>
       </c>
       <c r="I67" t="n">
         <v>547.7703057724306</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.27</v>
+        <v>-3.57</v>
       </c>
       <c r="L67" t="n">
-        <v>3.54</v>
+        <v>4.17</v>
       </c>
       <c r="M67" t="n">
         <v>2.83</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>10.02</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H68" t="n">
-        <v>512.8</v>
+        <v>501.5</v>
       </c>
       <c r="I68" t="n">
         <v>507.1476720142655</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K68" t="n">
-        <v>-6.56</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>9.42</v>
+        <v>11.26</v>
       </c>
       <c r="M68" t="n">
         <v>0.55</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>12.08</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H69" t="n">
-        <v>498.15</v>
+        <v>507.05</v>
       </c>
       <c r="I69" t="n">
         <v>506.584353214736</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K69" t="n">
-        <v>0.67</v>
+        <v>-1.11</v>
       </c>
       <c r="L69" t="n">
         <v>4.96</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>8.82</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="H70" t="n">
-        <v>544.95</v>
+        <v>533.95</v>
       </c>
       <c r="I70" t="n">
         <v>534.3766819057537</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K70" t="n">
-        <v>7.47</v>
+        <v>5.31</v>
       </c>
       <c r="L70" t="n">
         <v>5.27</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>10.57</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="H71" t="n">
-        <v>567.75</v>
+        <v>570.9</v>
       </c>
       <c r="I71" t="n">
         <v>568.7714171057444</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.33</v>
+        <v>-6.92</v>
       </c>
       <c r="L71" t="n">
-        <v>7.06</v>
+        <v>7.88</v>
       </c>
       <c r="M71" t="n">
         <v>2.38</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>6.56</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H72" t="n">
-        <v>545.05</v>
+        <v>532.8</v>
       </c>
       <c r="I72" t="n">
         <v>533.4330024423251</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K72" t="n">
-        <v>-4.53</v>
+        <v>-6.67</v>
       </c>
       <c r="L72" t="n">
-        <v>6.1</v>
+        <v>6.99</v>
       </c>
       <c r="M72" t="n">
         <v>1.34</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>7.6</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="H73" t="n">
-        <v>559.4</v>
+        <v>566.75</v>
       </c>
       <c r="I73" t="n">
         <v>565.2976471742721</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K73" t="n">
-        <v>-4.99</v>
+        <v>-6.37</v>
       </c>
       <c r="L73" t="n">
-        <v>5.63</v>
+        <v>6.87</v>
       </c>
       <c r="M73" t="n">
         <v>0.64</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>6.9</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H74" t="n">
-        <v>592.35</v>
+        <v>580</v>
       </c>
       <c r="I74" t="n">
         <v>587.8134393314851</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K74" t="n">
-        <v>4.52</v>
+        <v>2.34</v>
       </c>
       <c r="L74" t="n">
         <v>1.38</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>8.77</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="H75" t="n">
-        <v>556.35</v>
+        <v>559.65</v>
       </c>
       <c r="I75" t="n">
         <v>558.0568474889288</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K75" t="n">
-        <v>4.08</v>
+        <v>3.51</v>
       </c>
       <c r="L75" t="n">
         <v>4.39</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>6</v>
+      </c>
+      <c r="U75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>4.97</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H76" t="n">
-        <v>546.7</v>
+        <v>536.95</v>
       </c>
       <c r="I76" t="n">
         <v>544.2627118478173</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.31</v>
+        <v>-4.06</v>
       </c>
       <c r="L76" t="n">
-        <v>2.59</v>
+        <v>4.29</v>
       </c>
       <c r="M76" t="n">
         <v>-0</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.34</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H77" t="n">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="I77" t="n">
         <v>451.0487298343413</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K77" t="n">
-        <v>17.87</v>
+        <v>15.45</v>
       </c>
       <c r="L77" t="n">
         <v>4</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>11.77</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H78" t="n">
-        <v>426.35</v>
+        <v>417.55</v>
       </c>
       <c r="I78" t="n">
         <v>419.8504716008589</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K78" t="n">
-        <v>-6.09</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>7.25</v>
+        <v>8.59</v>
       </c>
       <c r="M78" t="n">
         <v>1.41</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>10.51</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="H79" t="n">
-        <v>428.95</v>
+        <v>443.4</v>
       </c>
       <c r="I79" t="n">
         <v>440.8038497942982</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.73</v>
+        <v>-6.19</v>
       </c>
       <c r="L79" t="n">
-        <v>4.39</v>
+        <v>6.38</v>
       </c>
       <c r="M79" t="n">
         <v>1.96</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H80" t="n">
-        <v>412.4</v>
+        <v>407.5</v>
       </c>
       <c r="I80" t="n">
         <v>411.1696613373899</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.99</v>
+        <v>-8.1</v>
       </c>
       <c r="L80" t="n">
-        <v>7.65</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M80" t="n">
         <v>1.48</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>48</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.1</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72.5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -10079,7 +11058,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -10089,7 +11068,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -10099,7 +11078,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="14">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.02</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.64</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.35</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.77</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.8</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.9</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.4</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="21">
@@ -10179,7 +11158,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.79</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="22">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="25">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.74</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="27">
@@ -10239,7 +11218,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.6</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="28">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
